--- a/specs/012-data-migration/overlap/新旧系统重叠数据确认报告.xlsx
+++ b/specs/012-data-migration/overlap/新旧系统重叠数据确认报告.xlsx
@@ -98,7 +98,9 @@
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -482,10 +484,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -517,7 +519,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>核心结论</t>
+          <t>本次迁移涉及的 5 个功能</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
@@ -525,58 +527,130 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>newpm 生产现状</t>
+          <t>① 批次版本管理</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>52 个任务(33个有任务号, 2025-2026) / 19 个批次(2026)；5功能业务表基本为空</t>
+          <t>出入库版本管理-批次版本</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>老 yadapm 历史数据</t>
+          <t>② 非批次版本管理</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>跨 2021-2026，约 7200 条业务记录，引用约 2900 任务 / 218 批次</t>
+          <t>出入库版本管理-非批次版本</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>任务重叠</t>
+          <t>③ 旧数据查询</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>老④引用202个去重任务，与生产仅重叠 7 个(其余195个生产没有)；其中2个为编号撞车</t>
+          <t>出入库版本管理-旧数据查询(历史归档)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>批次重叠</t>
+          <t>④ 批次任务问题单及缺陷</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>老218个批次，与生产仅重叠 5 个(其余213个生产没有)</t>
+          <t>项目质量管理-批次任务问题单及缺陷</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>⑤ 非批次任务问题单及缺陷</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>项目质量管理-非批次任务问题单及缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>核心结论</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>newpm 生产现状</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>52 个任务(33个有任务号, 2025-2026) / 19 个批次(2026)；上述5功能业务表基本为空</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>老 yadapm 历史数据</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>跨 2021-2026，约 7200 条业务记录，引用约 2900 任务 / 218 批次</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>任务重叠</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>老『批次任务问题单及缺陷』引用202个去重任务，与生产仅重叠 7 个(其余195个生产没有)；其中2个为编号撞车</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>批次重叠</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>老库218个批次，与生产仅重叠 5 个(其余213个生产没有)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>一句话</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>历史数据引用的任务/批次绝大多数在 newpm 不存在，迁移需业务方确认呈现策略</t>
         </is>
@@ -1033,7 +1107,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>④问题单引用的任务</t>
+          <t>批次任务问题单及缺陷-引用的任务</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
@@ -1154,7 +1228,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>占97%的『newpm没有的历史任务/批次』怎么呈现？ A反范式化(自带文本快照,推荐) / B注入老任务批次(污染日常任务管理) / C缩范围(先迁自包含功能)</t>
+          <t>占97%的『newpm没有的历史任务/批次』怎么呈现？ A反范式化(历史记录自带任务名/批次号文本快照,推荐) / B注入老任务批次(把老任务批次也导进系统,会污染日常任务管理) / C缩范围(先只迁自包含的功能:旧数据查询、非批次版本管理、非批次任务问题单及缺陷)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr"/>
@@ -1165,7 +1239,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>附件：老批次问题单仅47个附件、非批次0个，且物理文件不在备份(只有DB记录指向老服务器F:\路径)。是否需单独找老服务器要附件文件？</t>
+          <t>附件：老『批次任务问题单及缺陷』仅47个附件、『非批次任务问题单及缺陷』0个，且物理文件不在备份(只有DB记录指向老服务器F:\路径)。是否需单独找老服务器要附件文件？</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr"/>

--- a/specs/012-data-migration/overlap/新旧系统重叠数据确认报告.xlsx
+++ b/specs/012-data-migration/overlap/新旧系统重叠数据确认报告.xlsx
@@ -667,27 +667,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>任务号重叠（7个，需确认是否同一任务；同编号≠同任务）</t>
+          <t>任务号重叠（7个，需确认是否同一任务；新旧任务号并排,同编号≠同任务）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>任务编号</t>
+          <t>老系统任务号</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -697,15 +698,20 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>newpm任务号</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
           <t>newpm任务名称</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>系统判断</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>业务确认(请填)</t>
         </is>
@@ -724,18 +730,23 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
+          <t>M-202501-00030</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
           <t>商户管理整合项目[第3期]</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>✅名称一致 疑似同一</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>M-202510-00065</t>
         </is>
@@ -745,17 +756,22 @@
           <t>网络支付整合与能力提升项目[第55期]</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>M-202510-00065</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>TMS-【能力提升】-线下收单CRR086-273-201-中银智慧付静态二维码限额管理规则优化需求</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>❌名称不同 疑似编号撞车</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -770,18 +786,23 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
+          <t>M-202510-00632</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
           <t>24年专项分期监管及审计整改项目[第10期]</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>✅名称一致 疑似同一</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>M-202511-00610</t>
         </is>
@@ -791,17 +812,22 @@
           <t>网络支付整合与能力提升项目[第63期]</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>M-202511-00610</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>TMS【能力提升】-线下收单CRR086-211-提升系统处理银联二维码反扫交易的成功率</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>❌名称不同 疑似编号撞车</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -816,15 +842,20 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
+          <t>M-202512-00694</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
           <t>总对总汽车品牌购车线索管理及流程优化需求[第1期]</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>✅名称一致 疑似同一</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -839,15 +870,20 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
+          <t>M-202601-00522</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
           <t>商户管理整合项目[第19期]</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>✅名称一致 疑似同一</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -862,15 +898,20 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
+          <t>M-202601-00645</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
           <t>分行产品问题快速解决机制业务需求（中银智慧商家需求）[第4期]</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>✅名称一致 疑似同一</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
